--- a/Investment_Strategy_Example/Config/backtest_engine_parameters.xlsx
+++ b/Investment_Strategy_Example/Config/backtest_engine_parameters.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\KN Hack\Research-Challenge-2026\Investment_Strategy\Config\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\KN Hack\Research-Challenge-2026\Investment_Strategy_Example\Config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34F5C74B-1E56-4282-846B-81718E714D76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3201D224-6B40-44F1-A639-D22628D57480}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -826,7 +826,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="19">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>15</v>
